--- a/SuppXLS/Scen_A_SYS_SAD_40TS.xlsx
+++ b/SuppXLS/Scen_A_SYS_SAD_40TS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF072502-0476-4594-97D0-1C58F627CB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52FF735-2CD7-425A-9981-1CBE9E2C9C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="12" r:id="rId1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2866" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="146">
   <si>
     <t>~TFM_INS</t>
   </si>
@@ -593,17 +593,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1231,133 +1224,127 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="38" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="44" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="47" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="44" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="47" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="38" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="20% - Accent1" xfId="21" builtinId="30" customBuiltin="1"/>
@@ -2222,7 +2209,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2230,6 +2216,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2747,7 +2734,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2755,6 +2741,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2859,7 +2846,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-GB"/>
+          <a:endParaRPr lang="LID4096"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3593,7 +3580,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3601,6 +3587,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15307,7 +15294,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AE91"/>
+  <dimension ref="B1:AE42"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:31" x14ac:dyDescent="0.25">
@@ -15415,116 +15402,88 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <f>1-SUM(D4:D42)</f>
-        <v>2.1700000000000053E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:AE3" si="0">1-SUM(E4:E42)</f>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="F3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="G3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="H3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="I3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="J3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="K3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="L3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="M3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="N3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="O3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="P3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="R3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="S3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="T3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="U3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="V3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="W3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="X3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="AC3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="AD3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="0"/>
-        <v>2.163000000000026E-2</v>
+        <v>2.1575342465753398E-2</v>
       </c>
     </row>
     <row r="4" spans="2:31" x14ac:dyDescent="0.25">
@@ -15535,116 +15494,88 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <f>+ROUND(D53,4)</f>
-        <v>6.1999999999999998E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:AE13" si="1">+ROUND(E53,5)</f>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="F4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="G4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="H4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="I4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="J4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="L4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="M4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="O4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="P4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="S4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="T4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="U4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="V4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="W4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="X4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
     </row>
     <row r="5" spans="2:31" x14ac:dyDescent="0.25">
@@ -15655,116 +15586,88 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D42" si="2">+ROUND(D54,4)</f>
-        <v>2.47E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="D5:S42" si="3">+ROUND(E54,5)</f>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="F5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="G5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="H5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="I5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="J5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="K5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="L5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="M5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="N5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="O5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="P5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="R5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="S5">
-        <f t="shared" si="3"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="T5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="U5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="V5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="W5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="X5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
       <c r="AE5">
-        <f t="shared" si="1"/>
-        <v>2.4660000000000001E-2</v>
+        <v>2.46575342465753E-2</v>
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.25">
@@ -15775,116 +15678,88 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <f t="shared" si="2"/>
-        <v>6.1999999999999998E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="F6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="H6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="P6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="S6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="U6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="W6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="X6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="1"/>
-        <v>6.1599999999999997E-3</v>
+        <v>6.1643835616438398E-3</v>
       </c>
     </row>
     <row r="7" spans="2:31" x14ac:dyDescent="0.25">
@@ -15895,116 +15770,88 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <f t="shared" si="2"/>
-        <v>1.54E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="F7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="H7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="J7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="K7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="L7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="M7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="P7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="R7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="S7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="T7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="U7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="V7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="W7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="X7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="1"/>
-        <v>1.541E-2</v>
+        <v>1.54109589041096E-2</v>
       </c>
     </row>
     <row r="8" spans="2:31" x14ac:dyDescent="0.25">
@@ -16015,116 +15862,88 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <f t="shared" si="2"/>
-        <v>5.11E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="E8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="F8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="H8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="P8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="S8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="T8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="U8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="V8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="W8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="X8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="1"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
     </row>
     <row r="9" spans="2:31" x14ac:dyDescent="0.25">
@@ -16135,116 +15954,88 @@
         <v>32</v>
       </c>
       <c r="D9">
-        <f t="shared" si="2"/>
-        <v>1.46E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="F9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="G9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="H9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="I9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="J9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="K9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="M9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="P9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="R9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="S9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="T9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="U9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="V9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="W9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="X9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Z9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
     </row>
     <row r="10" spans="2:31" x14ac:dyDescent="0.25">
@@ -16255,116 +16046,88 @@
         <v>32</v>
       </c>
       <c r="D10">
-        <f t="shared" si="2"/>
-        <v>5.8400000000000001E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="E10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="F10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="G10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="H10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="I10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="J10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="K10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="L10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="M10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="P10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="S10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="T10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="U10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="V10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="W10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="X10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="1"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
     </row>
     <row r="11" spans="2:31" x14ac:dyDescent="0.25">
@@ -16375,116 +16138,88 @@
         <v>32</v>
       </c>
       <c r="D11">
-        <f t="shared" si="2"/>
-        <v>1.46E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="E11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="F11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="G11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="H11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="I11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="J11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="K11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="L11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="M11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="P11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="S11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="T11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="U11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="V11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="W11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="X11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="1"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.25">
@@ -16495,116 +16230,88 @@
         <v>32</v>
       </c>
       <c r="D12">
-        <f t="shared" si="2"/>
-        <v>3.6499999999999998E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="E12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="F12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="G12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="H12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="I12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="J12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="K12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="L12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="M12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="P12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="R12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="S12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="T12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="U12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="V12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="W12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="X12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="1"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.25">
@@ -16615,116 +16322,88 @@
         <v>32</v>
       </c>
       <c r="D13">
-        <f t="shared" si="2"/>
-        <v>2.3199999999999998E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="E13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="F13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="G13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="H13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="I13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="J13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="K13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="L13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="M13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="O13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="P13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="R13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="S13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="T13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="U13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="V13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="W13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="X13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="1"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.25">
@@ -16735,116 +16414,88 @@
         <v>32</v>
       </c>
       <c r="D14">
-        <f t="shared" si="2"/>
-        <v>6.6E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14:AE23" si="4">+ROUND(E63,5)</f>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="F14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="G14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="H14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="I14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="J14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="K14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="L14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="M14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="N14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="O14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="P14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="R14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="S14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="T14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="U14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="V14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="W14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="X14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.25">
@@ -16855,116 +16506,88 @@
         <v>32</v>
       </c>
       <c r="D15">
-        <f t="shared" si="2"/>
-        <v>2.6499999999999999E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="E15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="F15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="G15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="H15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="I15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="J15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="K15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="L15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="M15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="N15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="O15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="P15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="R15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="S15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="T15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="U15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="V15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="W15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="X15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="4"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.25">
@@ -16975,116 +16598,88 @@
         <v>32</v>
       </c>
       <c r="D16">
-        <f t="shared" si="2"/>
-        <v>6.6E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="E16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="F16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="G16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="H16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="I16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="J16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="K16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="L16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="M16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="N16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="O16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="P16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="R16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="S16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="T16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="U16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="V16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="W16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="X16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="4"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
     </row>
     <row r="17" spans="2:31" x14ac:dyDescent="0.25">
@@ -17095,116 +16690,88 @@
         <v>32</v>
       </c>
       <c r="D17">
-        <f t="shared" si="2"/>
-        <v>1.66E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="E17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="F17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="G17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="H17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="I17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="J17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="K17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="L17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="M17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="N17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="O17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="P17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="R17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="S17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="T17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="U17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="V17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="W17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="X17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AE17">
-        <f t="shared" si="4"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
     </row>
     <row r="18" spans="2:31" x14ac:dyDescent="0.25">
@@ -17215,116 +16782,88 @@
         <v>32</v>
       </c>
       <c r="D18">
-        <f t="shared" si="2"/>
-        <v>5.0299999999999997E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="E18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="F18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="G18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="H18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="I18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="J18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="K18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="L18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="M18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="N18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="O18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="P18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="R18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="S18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="T18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="U18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="V18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="W18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="X18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="Z18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="AD18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
       <c r="AE18">
-        <f t="shared" si="4"/>
-        <v>5.0340000000000003E-2</v>
+        <v>5.0342465753424701E-2</v>
       </c>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.25">
@@ -17335,116 +16874,88 @@
         <v>32</v>
       </c>
       <c r="D19">
-        <f t="shared" si="2"/>
-        <v>1.44E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="E19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="F19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="G19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="H19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="I19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="J19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="K19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="L19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="M19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="N19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="O19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="P19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="R19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="S19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="T19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="U19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="V19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="W19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="X19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="Z19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AD19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AE19">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.25">
@@ -17455,116 +16966,88 @@
         <v>32</v>
       </c>
       <c r="D20">
-        <f t="shared" si="2"/>
-        <v>5.7500000000000002E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="E20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="F20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="G20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="H20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="I20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="J20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="K20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="L20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="M20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="N20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="O20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="P20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="R20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="S20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="T20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="U20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="V20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="W20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="X20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="Z20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="AB20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="AC20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="AD20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
       <c r="AE20">
-        <f t="shared" si="4"/>
-        <v>5.7529999999999998E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
     </row>
     <row r="21" spans="2:31" x14ac:dyDescent="0.25">
@@ -17575,116 +17058,88 @@
         <v>32</v>
       </c>
       <c r="D21">
-        <f t="shared" si="2"/>
-        <v>1.44E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="E21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="F21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="G21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="H21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="I21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="J21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="K21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="L21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="M21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="N21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="O21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="P21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="R21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="S21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="T21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="U21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="V21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="W21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="X21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="Z21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AD21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
       <c r="AE21">
-        <f t="shared" si="4"/>
-        <v>1.438E-2</v>
+        <v>1.4383561643835601E-2</v>
       </c>
     </row>
     <row r="22" spans="2:31" x14ac:dyDescent="0.25">
@@ -17695,116 +17150,88 @@
         <v>32</v>
       </c>
       <c r="D22">
-        <f t="shared" si="2"/>
-        <v>3.5999999999999997E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="E22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="F22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="G22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="H22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="I22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="J22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="K22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="L22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="M22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="N22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="O22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="P22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="R22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="S22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="T22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="U22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="V22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="W22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="X22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="Z22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
       <c r="AE22">
-        <f t="shared" si="4"/>
-        <v>3.5959999999999999E-2</v>
+        <v>3.5958904109588997E-2</v>
       </c>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.25">
@@ -17815,116 +17242,88 @@
         <v>32</v>
       </c>
       <c r="D23">
-        <f t="shared" si="2"/>
-        <v>2.24E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="E23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="F23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="G23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="H23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="I23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="J23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="K23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="L23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="M23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="N23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="O23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="P23">
-        <f t="shared" si="4"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="Q23">
-        <f t="shared" ref="E23:AE32" si="5">+ROUND(Q72,5)</f>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="R23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="S23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="T23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="U23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="V23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="W23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="X23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="Z23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="AB23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="AC23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="AD23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
       <c r="AE23">
-        <f t="shared" si="5"/>
-        <v>2.2370000000000001E-2</v>
+        <v>2.2374429223744299E-2</v>
       </c>
     </row>
     <row r="24" spans="2:31" x14ac:dyDescent="0.25">
@@ -17935,116 +17334,88 @@
         <v>32</v>
       </c>
       <c r="D24">
-        <f t="shared" si="2"/>
-        <v>6.4000000000000003E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="E24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="F24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="G24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="H24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="I24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="J24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="K24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="L24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="M24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="N24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="O24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="P24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="R24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="S24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="T24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="U24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="V24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="W24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="X24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="Y24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="Z24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AA24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AB24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AC24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AD24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AE24">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.25">
@@ -18055,116 +17426,88 @@
         <v>32</v>
       </c>
       <c r="D25">
-        <f t="shared" si="2"/>
-        <v>2.5600000000000001E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="E25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="F25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="G25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="H25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="I25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="J25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="K25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="L25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="M25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="N25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="O25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="P25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="R25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="S25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="T25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="U25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="V25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="W25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="X25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="Z25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="AA25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="AB25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="AC25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="AD25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
       <c r="AE25">
-        <f t="shared" si="5"/>
-        <v>2.5569999999999999E-2</v>
+        <v>2.5570776255707799E-2</v>
       </c>
     </row>
     <row r="26" spans="2:31" x14ac:dyDescent="0.25">
@@ -18175,116 +17518,88 @@
         <v>32</v>
       </c>
       <c r="D26">
-        <f t="shared" si="2"/>
-        <v>6.4000000000000003E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="E26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="F26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="G26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="H26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="I26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="J26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="K26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="L26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="M26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="N26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="O26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="P26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="R26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="S26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="T26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="U26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="V26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="W26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="X26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="Y26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="Z26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AA26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AB26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AC26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AD26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
       <c r="AE26">
-        <f t="shared" si="5"/>
-        <v>6.3899999999999998E-3</v>
+        <v>6.3926940639269401E-3</v>
       </c>
     </row>
     <row r="27" spans="2:31" x14ac:dyDescent="0.25">
@@ -18295,116 +17610,88 @@
         <v>32</v>
       </c>
       <c r="D27">
-        <f t="shared" si="2"/>
-        <v>1.6E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="E27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="F27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="G27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="H27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="I27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="J27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="K27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="L27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="M27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="N27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="O27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="P27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="R27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="S27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="T27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="U27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="V27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="W27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="X27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="Y27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="Z27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="AA27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="AB27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="AC27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="AD27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
       <c r="AE27">
-        <f t="shared" si="5"/>
-        <v>1.5980000000000001E-2</v>
+        <v>1.5981735159817399E-2</v>
       </c>
     </row>
     <row r="28" spans="2:31" x14ac:dyDescent="0.25">
@@ -18415,116 +17702,88 @@
         <v>32</v>
       </c>
       <c r="D28">
-        <f t="shared" si="2"/>
-        <v>5.11E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="E28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="F28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="G28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="H28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="I28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="J28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="K28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="L28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="M28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="N28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="O28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="P28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="R28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="S28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="T28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="U28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="V28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="W28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="X28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="Y28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="Z28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AA28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AB28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AC28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AD28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
       <c r="AE28">
-        <f t="shared" si="5"/>
-        <v>5.1139999999999998E-2</v>
+        <v>5.11415525114155E-2</v>
       </c>
     </row>
     <row r="29" spans="2:31" x14ac:dyDescent="0.25">
@@ -18535,116 +17794,88 @@
         <v>32</v>
       </c>
       <c r="D29">
-        <f t="shared" si="2"/>
-        <v>1.46E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="E29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="F29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="G29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="H29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="I29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="J29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="K29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="L29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="M29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="N29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="O29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="P29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="R29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="S29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="T29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="U29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="V29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="W29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="X29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Y29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Z29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AA29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AB29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AC29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AD29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AE29">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
     </row>
     <row r="30" spans="2:31" x14ac:dyDescent="0.25">
@@ -18655,116 +17886,88 @@
         <v>32</v>
       </c>
       <c r="D30">
-        <f t="shared" si="2"/>
-        <v>5.8400000000000001E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="E30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="F30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="G30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="H30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="I30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="J30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="K30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="L30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="M30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="N30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="O30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="P30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="R30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="S30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="T30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="U30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="V30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="W30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="X30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="Y30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="Z30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AA30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AB30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AC30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AD30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
       <c r="AE30">
-        <f t="shared" si="5"/>
-        <v>5.8450000000000002E-2</v>
+        <v>5.8447488584474898E-2</v>
       </c>
     </row>
     <row r="31" spans="2:31" x14ac:dyDescent="0.25">
@@ -18775,116 +17978,88 @@
         <v>32</v>
       </c>
       <c r="D31">
-        <f t="shared" si="2"/>
-        <v>1.46E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="E31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="F31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="G31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="H31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="I31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="J31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="K31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="L31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="M31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="N31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="O31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="P31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="R31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="S31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="T31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="U31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="V31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="W31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="X31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Y31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="Z31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AA31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AB31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AC31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AD31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
       <c r="AE31">
-        <f t="shared" si="5"/>
-        <v>1.461E-2</v>
+        <v>1.46118721461187E-2</v>
       </c>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.25">
@@ -18895,116 +18070,88 @@
         <v>32</v>
       </c>
       <c r="D32">
-        <f t="shared" si="2"/>
-        <v>3.6499999999999998E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="E32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="F32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="G32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="H32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="I32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="J32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="K32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="L32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="M32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="N32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="O32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="P32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="R32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="S32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="T32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="U32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="V32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="W32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="X32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="Y32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="Z32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AA32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AB32">
-        <f t="shared" si="5"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AC32">
-        <f t="shared" ref="E32:AE42" si="6">+ROUND(AC81,5)</f>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AD32">
-        <f t="shared" si="6"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
       <c r="AE32">
-        <f t="shared" si="6"/>
-        <v>3.653E-2</v>
+        <v>3.6529680365296802E-2</v>
       </c>
     </row>
     <row r="33" spans="2:31" x14ac:dyDescent="0.25">
@@ -19015,116 +18162,88 @@
         <v>32</v>
       </c>
       <c r="D33">
-        <f t="shared" si="2"/>
-        <v>2.3199999999999998E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="E33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="F33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="G33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="H33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="I33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="J33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="K33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="L33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="M33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="N33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="O33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="P33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="R33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="S33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="T33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="U33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="V33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="W33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="X33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="Y33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="Z33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AA33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AB33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AC33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AD33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
       <c r="AE33">
-        <f t="shared" si="6"/>
-        <v>2.317E-2</v>
+        <v>2.3173515981735199E-2</v>
       </c>
     </row>
     <row r="34" spans="2:31" x14ac:dyDescent="0.25">
@@ -19135,116 +18254,88 @@
         <v>32</v>
       </c>
       <c r="D34">
-        <f t="shared" si="2"/>
-        <v>6.6E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="E34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="F34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="G34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="H34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="I34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="J34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="K34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="L34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="M34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="N34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="O34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="P34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="R34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="S34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="T34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="U34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="V34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="W34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="X34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Y34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Z34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AA34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AB34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AC34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AD34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AE34">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
     </row>
     <row r="35" spans="2:31" x14ac:dyDescent="0.25">
@@ -19255,116 +18346,88 @@
         <v>32</v>
       </c>
       <c r="D35">
-        <f t="shared" si="2"/>
-        <v>2.6499999999999999E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="E35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="F35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="G35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="H35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="I35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="J35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="K35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="L35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="M35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="N35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="O35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="P35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="R35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="S35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="T35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="U35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="V35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="W35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="X35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="Y35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="Z35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AA35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AB35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AC35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AD35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
       <c r="AE35">
-        <f t="shared" si="6"/>
-        <v>2.648E-2</v>
+        <v>2.64840182648402E-2</v>
       </c>
     </row>
     <row r="36" spans="2:31" x14ac:dyDescent="0.25">
@@ -19375,116 +18438,88 @@
         <v>32</v>
       </c>
       <c r="D36">
-        <f t="shared" si="2"/>
-        <v>6.6E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="E36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="F36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="G36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="H36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="I36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="J36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="K36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="L36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="M36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="N36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="O36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="P36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="R36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="S36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="T36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="U36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="V36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="W36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="X36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Y36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="Z36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AA36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AB36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AC36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AD36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
       <c r="AE36">
-        <f t="shared" si="6"/>
-        <v>6.62E-3</v>
+        <v>6.62100456621005E-3</v>
       </c>
     </row>
     <row r="37" spans="2:31" x14ac:dyDescent="0.25">
@@ -19495,116 +18530,88 @@
         <v>32</v>
       </c>
       <c r="D37">
-        <f t="shared" si="2"/>
-        <v>1.66E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="E37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="F37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="G37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="H37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="I37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="J37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="K37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="L37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="M37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="N37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="O37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="P37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="R37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="S37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="T37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="U37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="V37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="W37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="X37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="Y37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="Z37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AA37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AB37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AC37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AD37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
       <c r="AE37">
-        <f t="shared" si="6"/>
-        <v>1.6549999999999999E-2</v>
+        <v>1.6552511415525099E-2</v>
       </c>
     </row>
     <row r="38" spans="2:31" x14ac:dyDescent="0.25">
@@ -19615,116 +18622,88 @@
         <v>32</v>
       </c>
       <c r="D38">
-        <f t="shared" si="2"/>
-        <v>4.87E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="E38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="F38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="G38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="H38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="I38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="J38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="K38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="L38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="M38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="N38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="O38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="P38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="R38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="S38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="T38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="U38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="V38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="W38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="X38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="Y38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="Z38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="AA38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="AB38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="AC38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="AD38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
       <c r="AE38">
-        <f t="shared" si="6"/>
-        <v>4.8739999999999999E-2</v>
+        <v>4.87442922374429E-2</v>
       </c>
     </row>
     <row r="39" spans="2:31" x14ac:dyDescent="0.25">
@@ -19735,116 +18714,88 @@
         <v>32</v>
       </c>
       <c r="D39">
-        <f t="shared" si="2"/>
-        <v>1.3899999999999999E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="E39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="F39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="G39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="H39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="I39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="J39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="K39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="L39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="M39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="N39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="O39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="P39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="Q39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="R39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="S39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="T39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="U39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="V39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="W39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="X39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="Y39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="Z39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AA39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AB39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AC39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AD39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AE39">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.25">
@@ -19855,116 +18806,88 @@
         <v>32</v>
       </c>
       <c r="D40">
-        <f t="shared" si="2"/>
-        <v>5.57E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="E40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="F40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="G40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="H40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="I40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="J40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="K40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="L40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="M40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="N40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="O40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="P40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="Q40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="R40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="S40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="T40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="U40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="V40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="W40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="X40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="Y40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="Z40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="AA40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="AB40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="AC40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="AD40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
       <c r="AE40">
-        <f t="shared" si="6"/>
-        <v>5.5710000000000003E-2</v>
+        <v>5.57077625570776E-2</v>
       </c>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.25">
@@ -19975,116 +18898,88 @@
         <v>32</v>
       </c>
       <c r="D41">
-        <f t="shared" si="2"/>
-        <v>1.3899999999999999E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="E41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="F41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="G41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="H41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="I41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="J41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="K41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="L41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="M41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="N41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="O41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="P41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="Q41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="R41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="S41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="T41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="U41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="V41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="W41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="X41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="Y41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="Z41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AA41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AB41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AC41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AD41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
       <c r="AE41">
-        <f t="shared" si="6"/>
-        <v>1.393E-2</v>
+        <v>1.39269406392694E-2</v>
       </c>
     </row>
     <row r="42" spans="2:31" x14ac:dyDescent="0.25">
@@ -20095,3795 +18990,87 @@
         <v>32</v>
       </c>
       <c r="D42">
-        <f t="shared" si="2"/>
-        <v>3.4799999999999998E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="E42">
-        <f t="shared" si="6"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="F42">
-        <f t="shared" si="6"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="G42">
-        <f t="shared" si="6"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="H42">
-        <f t="shared" si="6"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="I42">
-        <f t="shared" si="6"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="J42">
-        <f t="shared" si="6"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="K42">
-        <f t="shared" si="6"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="L42">
-        <f t="shared" si="6"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="M42">
-        <f t="shared" si="6"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="N42">
-        <f t="shared" ref="N42:AE42" si="7">+ROUND(N91,5)</f>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="O42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="P42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="Q42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="R42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="S42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="T42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="U42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="V42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="W42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="X42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="Y42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="Z42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="AA42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="AB42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="AC42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="AD42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
+        <v>3.48173515981735E-2</v>
       </c>
       <c r="AE42">
-        <f t="shared" si="7"/>
-        <v>3.4819999999999997E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B52" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="E52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="F52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="G52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="H52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="I52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="J52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="K52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="L52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="M52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="N52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="O52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="P52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="Q52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="R52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="S52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="T52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="U52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="V52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="W52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="X52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="Y52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="Z52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="AA52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="AB52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="AC52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="AD52" s="36">
-        <v>2.1575342465753398E-2</v>
-      </c>
-      <c r="AE52" s="39">
-        <v>2.1575342465753398E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B53" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="C53" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="E53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="F53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="G53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="H53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="I53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="J53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="K53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="L53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="M53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="N53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="O53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="P53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="Q53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="R53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="S53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="T53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="U53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="V53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="W53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="X53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="Y53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="Z53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AA53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AB53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AC53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AD53" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AE53" s="40">
-        <v>6.1643835616438398E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B54" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C54" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="E54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="F54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="G54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="H54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="I54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="J54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="K54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="L54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="M54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="N54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="O54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="P54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="Q54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="R54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="S54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="T54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="U54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="V54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="W54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="X54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="Y54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="Z54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="AA54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="AB54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="AC54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="AD54" s="36">
-        <v>2.46575342465753E-2</v>
-      </c>
-      <c r="AE54" s="39">
-        <v>2.46575342465753E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B55" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="E55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="F55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="G55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="H55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="I55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="J55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="K55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="L55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="M55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="N55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="O55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="P55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="Q55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="R55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="S55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="T55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="U55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="V55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="W55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="X55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="Y55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="Z55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AA55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AB55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AC55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AD55" s="38">
-        <v>6.1643835616438398E-3</v>
-      </c>
-      <c r="AE55" s="40">
-        <v>6.1643835616438398E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B56" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C56" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="E56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="F56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="G56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="H56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="I56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="J56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="K56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="L56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="M56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="N56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="O56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="P56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="Q56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="R56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="S56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="T56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="U56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="V56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="W56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="X56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="Y56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="Z56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="AA56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="AB56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="AC56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="AD56" s="36">
-        <v>1.54109589041096E-2</v>
-      </c>
-      <c r="AE56" s="39">
-        <v>1.54109589041096E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B57" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="C57" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="E57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="F57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="G57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="H57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="I57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="J57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="K57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="L57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="M57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="N57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="O57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="P57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="Q57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="R57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="S57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="T57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="U57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="V57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="W57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="X57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="Y57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="Z57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AA57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AB57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AC57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AD57" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AE57" s="40">
-        <v>5.11415525114155E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B58" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C58" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="E58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="F58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="G58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="H58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="I58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="J58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="K58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="L58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="M58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="N58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="O58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="P58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Q58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="R58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="S58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="T58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="U58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="V58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="W58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="X58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Y58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Z58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AA58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AB58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AC58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AD58" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AE58" s="39">
-        <v>1.46118721461187E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B59" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="E59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="F59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="G59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="H59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="I59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="J59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="K59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="L59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="M59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="N59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="O59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="P59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="Q59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="R59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="S59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="T59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="U59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="V59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="W59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="X59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="Y59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="Z59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AA59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AB59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AC59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AD59" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AE59" s="40">
-        <v>5.8447488584474898E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B60" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C60" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="E60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="F60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="G60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="H60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="I60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="J60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="K60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="L60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="M60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="N60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="O60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="P60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Q60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="R60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="S60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="T60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="U60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="V60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="W60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="X60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Y60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Z60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AA60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AB60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AC60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AD60" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AE60" s="39">
-        <v>1.46118721461187E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B61" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C61" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="E61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="F61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="G61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="H61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="I61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="J61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="K61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="L61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="M61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="N61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="O61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="P61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="Q61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="R61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="S61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="T61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="U61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="V61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="W61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="X61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="Y61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="Z61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AA61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AB61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AC61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AD61" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AE61" s="40">
-        <v>3.6529680365296802E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B62" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="C62" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="E62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="F62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="G62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="H62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="I62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="J62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="K62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="L62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="M62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="N62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="O62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="P62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="Q62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="R62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="S62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="T62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="U62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="V62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="W62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="X62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="Y62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="Z62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AA62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AB62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AC62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AD62" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AE62" s="39">
-        <v>2.3173515981735199E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B63" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C63" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="E63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="F63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="G63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="H63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="I63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="J63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="K63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="L63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="M63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="N63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="O63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="P63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Q63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="R63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="S63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="T63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="U63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="V63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="W63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="X63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Y63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Z63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AA63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AB63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AC63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AD63" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AE63" s="40">
-        <v>6.62100456621005E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B64" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C64" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="E64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="F64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="G64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="H64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="I64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="J64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="K64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="L64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="M64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="N64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="O64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="P64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="Q64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="R64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="S64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="T64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="U64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="V64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="W64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="X64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="Y64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="Z64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AA64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AB64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AC64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AD64" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AE64" s="39">
-        <v>2.64840182648402E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B65" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="C65" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="E65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="F65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="G65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="H65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="I65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="J65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="K65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="L65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="M65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="N65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="O65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="P65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Q65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="R65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="S65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="T65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="U65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="V65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="W65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="X65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Y65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Z65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AA65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AB65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AC65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AD65" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AE65" s="40">
-        <v>6.62100456621005E-3</v>
-      </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B66" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="E66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="F66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="G66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="H66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="I66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="J66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="K66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="L66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="M66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="N66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="O66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="P66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="Q66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="R66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="S66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="T66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="U66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="V66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="W66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="X66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="Y66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="Z66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AA66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AB66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AC66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AD66" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AE66" s="39">
-        <v>1.6552511415525099E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B67" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C67" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="E67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="F67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="G67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="H67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="I67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="J67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="K67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="L67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="M67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="N67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="O67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="P67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="Q67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="R67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="S67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="T67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="U67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="V67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="W67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="X67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="Y67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="Z67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="AA67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="AB67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="AC67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="AD67" s="38">
-        <v>5.0342465753424701E-2</v>
-      </c>
-      <c r="AE67" s="40">
-        <v>5.0342465753424701E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B68" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C68" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="E68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="F68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="G68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="H68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="I68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="J68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="K68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="L68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="M68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="N68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="O68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="P68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="Q68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="R68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="S68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="T68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="U68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="V68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="W68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="X68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="Y68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="Z68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AA68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AB68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AC68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AD68" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AE68" s="39">
-        <v>1.4383561643835601E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B69" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="C69" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="E69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="F69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="G69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="H69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="I69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="J69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="K69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="L69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="M69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="N69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="O69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="P69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="Q69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="R69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="S69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="T69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="U69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="V69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="W69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="X69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="Y69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="Z69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="AA69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="AB69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="AC69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="AD69" s="38">
-        <v>5.75342465753425E-2</v>
-      </c>
-      <c r="AE69" s="40">
-        <v>5.75342465753425E-2</v>
-      </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B70" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C70" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="E70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="F70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="G70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="H70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="I70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="J70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="K70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="L70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="M70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="N70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="O70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="P70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="Q70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="R70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="S70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="T70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="U70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="V70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="W70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="X70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="Y70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="Z70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AA70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AB70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AC70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AD70" s="36">
-        <v>1.4383561643835601E-2</v>
-      </c>
-      <c r="AE70" s="39">
-        <v>1.4383561643835601E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B71" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C71" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="E71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="F71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="G71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="H71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="I71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="J71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="K71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="L71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="M71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="N71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="O71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="P71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="Q71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="R71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="S71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="T71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="U71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="V71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="W71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="X71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="Y71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="Z71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="AA71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="AB71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="AC71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="AD71" s="38">
-        <v>3.5958904109588997E-2</v>
-      </c>
-      <c r="AE71" s="40">
-        <v>3.5958904109588997E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B72" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C72" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="E72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="F72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="G72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="H72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="I72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="J72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="K72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="L72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="M72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="N72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="O72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="P72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="Q72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="R72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="S72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="T72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="U72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="V72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="W72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="X72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="Y72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="Z72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="AA72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="AB72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="AC72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="AD72" s="36">
-        <v>2.2374429223744299E-2</v>
-      </c>
-      <c r="AE72" s="39">
-        <v>2.2374429223744299E-2</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B73" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C73" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="E73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="F73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="G73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="H73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="I73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="J73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="K73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="L73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="M73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="N73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="O73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="P73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="Q73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="R73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="S73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="T73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="U73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="V73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="W73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="X73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="Y73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="Z73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AA73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AB73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AC73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AD73" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AE73" s="40">
-        <v>6.3926940639269401E-3</v>
-      </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B74" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C74" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="E74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="F74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="G74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="H74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="I74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="J74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="K74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="L74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="M74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="N74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="O74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="P74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="Q74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="R74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="S74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="T74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="U74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="V74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="W74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="X74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="Y74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="Z74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="AA74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="AB74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="AC74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="AD74" s="36">
-        <v>2.5570776255707799E-2</v>
-      </c>
-      <c r="AE74" s="39">
-        <v>2.5570776255707799E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B75" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="C75" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="E75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="F75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="G75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="H75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="I75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="J75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="K75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="L75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="M75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="N75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="O75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="P75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="Q75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="R75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="S75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="T75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="U75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="V75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="W75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="X75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="Y75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="Z75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AA75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AB75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AC75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AD75" s="38">
-        <v>6.3926940639269401E-3</v>
-      </c>
-      <c r="AE75" s="40">
-        <v>6.3926940639269401E-3</v>
-      </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B76" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="C76" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="E76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="F76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="G76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="H76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="I76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="J76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="K76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="L76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="M76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="N76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="O76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="P76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="Q76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="R76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="S76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="T76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="U76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="V76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="W76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="X76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="Y76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="Z76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="AA76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="AB76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="AC76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="AD76" s="36">
-        <v>1.5981735159817399E-2</v>
-      </c>
-      <c r="AE76" s="39">
-        <v>1.5981735159817399E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B77" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="C77" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="E77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="F77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="G77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="H77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="I77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="J77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="K77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="L77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="M77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="N77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="O77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="P77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="Q77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="R77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="S77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="T77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="U77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="V77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="W77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="X77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="Y77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="Z77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AA77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AB77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AC77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AD77" s="38">
-        <v>5.11415525114155E-2</v>
-      </c>
-      <c r="AE77" s="40">
-        <v>5.11415525114155E-2</v>
-      </c>
-    </row>
-    <row r="78" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B78" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C78" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="E78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="F78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="G78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="H78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="I78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="J78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="K78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="L78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="M78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="N78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="O78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="P78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Q78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="R78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="S78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="T78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="U78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="V78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="W78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="X78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Y78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Z78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AA78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AB78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AC78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AD78" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AE78" s="39">
-        <v>1.46118721461187E-2</v>
-      </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B79" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="C79" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="E79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="F79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="G79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="H79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="I79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="J79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="K79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="L79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="M79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="N79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="O79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="P79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="Q79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="R79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="S79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="T79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="U79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="V79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="W79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="X79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="Y79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="Z79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AA79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AB79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AC79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AD79" s="38">
-        <v>5.8447488584474898E-2</v>
-      </c>
-      <c r="AE79" s="40">
-        <v>5.8447488584474898E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B80" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C80" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="E80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="F80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="G80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="H80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="I80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="J80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="K80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="L80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="M80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="N80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="O80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="P80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Q80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="R80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="S80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="T80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="U80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="V80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="W80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="X80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Y80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="Z80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AA80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AB80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AC80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AD80" s="36">
-        <v>1.46118721461187E-2</v>
-      </c>
-      <c r="AE80" s="39">
-        <v>1.46118721461187E-2</v>
-      </c>
-    </row>
-    <row r="81" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B81" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C81" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="E81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="F81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="G81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="H81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="I81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="J81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="K81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="L81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="M81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="N81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="O81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="P81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="Q81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="R81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="S81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="T81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="U81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="V81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="W81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="X81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="Y81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="Z81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AA81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AB81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AC81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AD81" s="38">
-        <v>3.6529680365296802E-2</v>
-      </c>
-      <c r="AE81" s="40">
-        <v>3.6529680365296802E-2</v>
-      </c>
-    </row>
-    <row r="82" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B82" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="C82" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="E82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="F82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="G82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="H82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="I82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="J82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="K82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="L82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="M82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="N82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="O82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="P82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="Q82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="R82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="S82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="T82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="U82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="V82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="W82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="X82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="Y82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="Z82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AA82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AB82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AC82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AD82" s="36">
-        <v>2.3173515981735199E-2</v>
-      </c>
-      <c r="AE82" s="39">
-        <v>2.3173515981735199E-2</v>
-      </c>
-    </row>
-    <row r="83" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B83" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C83" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="E83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="F83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="G83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="H83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="I83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="J83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="K83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="L83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="M83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="N83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="O83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="P83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Q83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="R83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="S83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="T83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="U83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="V83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="W83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="X83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Y83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Z83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AA83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AB83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AC83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AD83" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AE83" s="40">
-        <v>6.62100456621005E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B84" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="C84" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="E84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="F84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="G84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="H84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="I84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="J84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="K84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="L84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="M84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="N84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="O84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="P84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="Q84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="R84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="S84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="T84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="U84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="V84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="W84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="X84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="Y84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="Z84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AA84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AB84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AC84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AD84" s="36">
-        <v>2.64840182648402E-2</v>
-      </c>
-      <c r="AE84" s="39">
-        <v>2.64840182648402E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B85" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="C85" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="E85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="F85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="G85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="H85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="I85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="J85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="K85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="L85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="M85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="N85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="O85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="P85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Q85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="R85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="S85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="T85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="U85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="V85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="W85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="X85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Y85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="Z85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AA85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AB85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AC85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AD85" s="38">
-        <v>6.62100456621005E-3</v>
-      </c>
-      <c r="AE85" s="40">
-        <v>6.62100456621005E-3</v>
-      </c>
-    </row>
-    <row r="86" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B86" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C86" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="E86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="F86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="G86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="H86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="I86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="J86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="K86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="L86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="M86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="N86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="O86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="P86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="Q86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="R86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="S86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="T86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="U86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="V86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="W86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="X86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="Y86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="Z86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AA86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AB86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AC86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AD86" s="36">
-        <v>1.6552511415525099E-2</v>
-      </c>
-      <c r="AE86" s="39">
-        <v>1.6552511415525099E-2</v>
-      </c>
-    </row>
-    <row r="87" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B87" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C87" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="E87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="F87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="G87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="H87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="I87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="J87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="K87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="L87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="M87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="N87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="O87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="P87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="Q87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="R87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="S87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="T87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="U87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="V87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="W87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="X87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="Y87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="Z87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="AA87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="AB87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="AC87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="AD87" s="38">
-        <v>4.87442922374429E-2</v>
-      </c>
-      <c r="AE87" s="40">
-        <v>4.87442922374429E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B88" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C88" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="E88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="F88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="G88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="H88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="I88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="J88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="K88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="L88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="M88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="N88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="O88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="P88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="Q88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="R88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="S88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="T88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="U88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="V88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="W88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="X88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="Y88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="Z88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AA88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AB88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AC88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AD88" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AE88" s="39">
-        <v>1.39269406392694E-2</v>
-      </c>
-    </row>
-    <row r="89" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B89" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C89" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="E89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="F89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="G89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="H89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="I89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="J89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="K89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="L89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="M89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="N89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="O89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="P89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="Q89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="R89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="S89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="T89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="U89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="V89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="W89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="X89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="Y89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="Z89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="AA89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="AB89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="AC89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="AD89" s="38">
-        <v>5.57077625570776E-2</v>
-      </c>
-      <c r="AE89" s="40">
-        <v>5.57077625570776E-2</v>
-      </c>
-    </row>
-    <row r="90" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B90" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C90" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="E90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="F90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="G90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="H90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="I90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="J90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="K90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="L90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="M90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="N90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="O90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="P90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="Q90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="R90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="S90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="T90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="U90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="V90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="W90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="X90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="Y90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="Z90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AA90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AB90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AC90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AD90" s="36">
-        <v>1.39269406392694E-2</v>
-      </c>
-      <c r="AE90" s="39">
-        <v>1.39269406392694E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B91" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C91" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="E91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="F91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="G91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="H91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="I91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="J91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="K91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="L91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="M91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="N91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="O91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="P91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="Q91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="R91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="S91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="T91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="U91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="V91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="W91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="X91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="Y91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="Z91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="AA91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="AB91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="AC91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="AD91" s="38">
-        <v>3.48173515981735E-2</v>
-      </c>
-      <c r="AE91" s="40">
         <v>3.48173515981735E-2</v>
       </c>
     </row>
